--- a/survey_templates/039_child_speech_evaluation_survey--survey_templates.xlsx
+++ b/survey_templates/039_child_speech_evaluation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -939,8 +939,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -968,12 +968,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'under_12_months',_'value':_'early'}</t>
+          <t>under_12_months</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Under 12 months', 'value': 'early'}</t>
+          <t>Under 12 months</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'12_to_18_months',_'value':_'average'}</t>
+          <t>12_to_18_months</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '12 to 18 months', 'value': 'average'}</t>
+          <t>12 to 18 months</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'18_to_24_months',_'value':_'late'}</t>
+          <t>18_to_24_months</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '18 to 24 months', 'value': 'late'}</t>
+          <t>18 to 24 months</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'over_24_months',_'value':_'delayed'}</t>
+          <t>over_24_months</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Over 24 months', 'value': 'delayed'}</t>
+          <t>Over 24 months</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'not_yet_speaking',_'value':_'none'}</t>
+          <t>not_yet_speaking</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Not yet speaking', 'value': 'none'}</t>
+          <t>Not yet speaking</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_frequently',_'value':_'frequent'}</t>
+          <t>yes_-_frequently</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Frequently', 'value': 'frequent'}</t>
+          <t>Yes - Frequently</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_sometimes',_'value':_'occasional'}</t>
+          <t>yes_-_sometimes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Sometimes', 'value': 'occasional'}</t>
+          <t>Yes - Sometimes</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_single_words_only',_'value':_'single'}</t>
+          <t>no_-_single_words_only</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'No - Single words only', 'value': 'single'}</t>
+          <t>No - Single words only</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'100_percent_-_clear',_'value':_'100'}</t>
+          <t>100_percent_-_clear</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '100 percent - Clear', 'value': '100'}</t>
+          <t>100 percent - Clear</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'75_percent_-_mostly_clear',_'value':_'75'}</t>
+          <t>75_percent_-_mostly_clear</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '75 percent - Mostly clear', 'value': '75'}</t>
+          <t>75 percent - Mostly clear</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'50_percent_-_partial_understanding',_'value':_'50'}</t>
+          <t>50_percent_-_partial_understanding</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '50 percent - Partial understanding', 'value': '50'}</t>
+          <t>50 percent - Partial understanding</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_25_percent_-_difficult',_'value':_'25'}</t>
+          <t>less_than_25_percent_-_difficult</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 25 percent - Difficult', 'value': '25'}</t>
+          <t>Less than 25 percent - Difficult</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'100_percent_-_clear',_'value':_'100'}</t>
+          <t>100_percent_-_clear</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '100 percent - Clear', 'value': '100'}</t>
+          <t>100 percent - Clear</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'75_percent_-_mostly_clear',_'value':_'75'}</t>
+          <t>75_percent_-_mostly_clear</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '75 percent - Mostly clear', 'value': '75'}</t>
+          <t>75 percent - Mostly clear</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'50_percent_-_partial_understanding',_'value':_'50'}</t>
+          <t>50_percent_-_partial_understanding</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '50 percent - Partial understanding', 'value': '50'}</t>
+          <t>50 percent - Partial understanding</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_25_percent_-_difficult',_'value':_'25'}</t>
+          <t>less_than_25_percent_-_difficult</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 25 percent - Difficult', 'value': '25'}</t>
+          <t>Less than 25 percent - Difficult</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_consistent',_'value':_true}</t>
+          <t>yes_-_consistent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Consistent', 'value': True}</t>
+          <t>Yes - Consistent</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes', 'value': 'sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_rarely',_'value':_false}</t>
+          <t>no_-_rarely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'No - Rarely', 'value': False}</t>
+          <t>No - Rarely</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_always',_'value':_true}</t>
+          <t>yes_-_always</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Always', 'value': True}</t>
+          <t>Yes - Always</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_inconsistent',_'value':_false}</t>
+          <t>no_-_inconsistent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'No - Inconsistent', 'value': False}</t>
+          <t>No - Inconsistent</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_recent_test',_'value':_true}</t>
+          <t>yes_-_recent_test</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Recent test', 'value': True}</t>
+          <t>Yes - Recent test</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_not_tested',_'value':_false}</t>
+          <t>no_-_not_tested</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'No - Not tested', 'value': False}</t>
+          <t>No - Not tested</t>
         </is>
       </c>
     </row>
